--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>165.</t>
+          <t>175.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>669.</t>
+          <t>679.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>752.</t>
+          <t>756.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>175.</t>
+          <t>261.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>679.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>756.</t>
+          <t>773.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>261.</t>
+          <t>378.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>810.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>773.</t>
+          <t>853.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>378.</t>
+          <t>494.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>810.</t>
+          <t>905.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>08-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>18-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -572,81 +572,23 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>PWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>3,87,50,583</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>59782330</v>
+        <v>38750583</v>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Himachal eTenders</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>853.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PWD</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3,87,50,583</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>38750583</v>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>494.</t>
+          <t>631.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,64 +533,6 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Himachal eTenders</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>905.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PWD</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3,87,50,583</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>38750583</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>
       </c>
     </row>

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>631.</t>
+          <t>636.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>636.</t>
+          <t>702.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>702.</t>
+          <t>703.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>703.</t>
+          <t>806.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -490,49 +490,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>806.</t>
+          <t>377.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>23-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>04-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>6,07,83,682</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>27952391</v>
+        <v>60783682</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
         </is>
       </c>
     </row>

--- a/himachal_etenders.xlsx
+++ b/himachal_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,58 +481,232 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>46.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Safety tank, Rain water harvesting tank, Heliport, Site development, overhead tank, Hanger, watch Tower, Security hut and approach road, providing E.I. Fire ] [Job1 Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Sa][2026_PWD_137756_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14,39,13,728</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>143913728</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc1jGj5kxAFe9wiyhRytfLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Review Tender</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Himachal eTenders</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>471.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[Construction of Sub-Tehsil Building at Majheen, Distt.Kangra(H.P)] [1514-15 dated 0206.2026][2026_PWD_137564_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1,12,64,584</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>11264584</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCGn9fBlgLprVNPXsoOHr6w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>32</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>377.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>691.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>23-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>04-Jul-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>6,07,83,682</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K4" t="n">
         <v>60783682</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>101.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 05:30 PM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>05-Aug-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>07-Aug-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Setting up of ASU and Supply of Medical oxygen] [E-tender of Air Separation Unit ][2026_DMER5_137839_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Directorate of Medical Education and Research||Dr Rajendra Prasad Govt Medical College Tanda Kangra</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5cZtX41mGcgxuk1aO1fnGg%3D%3D</t>
         </is>
       </c>
     </row>
